--- a/data/Components.xlsx
+++ b/data/Components.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suibianluanchi/codegit/FiberOptic Network Design and Link Analysis/components/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suibianluanchi/codegit/FiberOptic Network Design and Link Analysis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C323B2C-C0CE-AC45-B3B4-DCCF820A5394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BC956DD-4BC4-7C41-944B-A57C7056EB1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="86">
   <si>
     <t>Fiber</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -374,12 +375,20 @@
     <t>-128dB/Hz</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>MUX/DEMUX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FS #26569 — 16-channel DWDM MUX/DEMUX, 100 GHz, C27–C42, dual-fiber</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -429,6 +438,12 @@
       <family val="1"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -463,7 +478,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -492,6 +507,8 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1160,4 +1177,59 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A17E46BC-986C-BE4F-BC29-FB8F8FCA9DB1}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <cols>
+    <col min="1" max="1" width="22.1640625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="21.1640625" style="10" customWidth="1"/>
+    <col min="3" max="16384" width="10.83203125" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" s="11" customFormat="1">
+      <c r="A3" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="C4" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="C5" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="11" customFormat="1">
+      <c r="A8" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="B9" s="10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>